--- a/DadosMetais/PCA-GPR-VSG/Results-no-vs.xlsx
+++ b/DadosMetais/PCA-GPR-VSG/Results-no-vs.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:J9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,120 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>89214.70849999999</v>
+      </c>
+      <c r="B7" t="n">
+        <v>86767.1603</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.5249</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.3912</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" t="n">
+        <v>3</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Fe</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>[[[0.09889999777078629], [0.4747999906539917], [-0.6409000158309937], [-0.05090000107884407], [0.4564000070095062], [-0.5339000225067139], [-0.19939999282360077], [-0.026000000536441803], [0.23669999837875366], [-0.3610000014305115]], [0.0], [[-0.6837000250816345]], [0.0]]</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>[[[-0.0714000016450882], [0.3458000123500824], [-0.8754000067710876], [0.16830000281333923], [0.32659998536109924], [-0.41589999198913574], [-0.3255999982357025], [-0.07280000299215317], [0.10360000282526016], [-0.387800008058548]], [0.1428000032901764], [[-0.7506999969482422]], [0.2061000019311905]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>329202.3337</v>
+      </c>
+      <c r="B8" t="n">
+        <v>452039.7728</v>
+      </c>
+      <c r="C8" t="n">
+        <v>-0.7533</v>
+      </c>
+      <c r="D8" t="n">
+        <v>-2.1719</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" t="n">
+        <v>4</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Fe</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>[[[-0.7318000197410583], [0.2628999948501587], [-0.5910999774932861], [0.2549999952316284], [0.1054999977350235], [-0.32670000195503235], [0.33880001306533813], [0.5248000025749207], [0.5349000096321106], [0.07259999960660934]], [0.0], [[1.506700038909912]], [0.0]]</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>[[[-0.6571000218391418], [0.25780001282691956], [-0.4772000014781952], [0.14910000562667847], [0.10019999742507935], [-0.3172999918460846], [0.32429999113082886], [0.43070000410079956], [0.6061999797821045], [0.16410000622272491]], [-0.10509999841451645], [[1.4086999893188477]], [-0.1054999977350235]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>4820.5985</v>
+      </c>
+      <c r="B9" t="n">
+        <v>22364.15</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.889</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.8431</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" t="n">
+        <v>2</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Fe</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>[[[0.6543999910354614], [-0.07450000196695328], [0.5468000173568726], [0.08609999716281891], [-0.37059998512268066], [0.6137999892234802], [-0.49950000643730164], [0.3727000057697296], [-0.5922999978065491], [-0.1898999959230423]], [0.0], [[1.2549999952316284]], [0.0]]</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>[[[0.12489999830722809], [0.13619999587535858], [0.9222999811172485], [-0.26350000500679016], [-0.1720999926328659], [0.25459998846054077], [-0.25529998540878296], [-0.009600000455975533], [0.2037000060081482], [-0.07750000059604645]], [1.0543999671936035], [[1.1644999980926514]], [-1.304900050163269]]</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
